--- a/resultados/third_review/20260907_data2024_race_colour.xlsx
+++ b/resultados/third_review/20260907_data2024_race_colour.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">race_colour</t>
   </si>
@@ -27,9 +27,6 @@
   </si>
   <si>
     <t xml:space="preserve">Brown (Parda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not informed</t>
   </si>
   <si>
     <t xml:space="preserve">Black (Preta)</t>
@@ -383,10 +380,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2142</v>
+        <v>2371</v>
       </c>
       <c r="C2" t="n">
-        <v>50.63</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +391,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>1363</v>
+        <v>1563</v>
       </c>
       <c r="C3" t="n">
-        <v>32.21</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +402,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>468</v>
+        <v>218</v>
       </c>
       <c r="C4" t="n">
-        <v>11.06</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +413,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>4.3</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="6">
@@ -427,20 +424,9 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>4231</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4231</v>
-      </c>
-      <c r="C7" t="n">
         <v>100</v>
       </c>
     </row>
